--- a/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65123_completo.xlsx
+++ b/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65123_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R78585a5f24924387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4faffad6393449d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,546 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.1102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.1302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65123_completo.xlsx
+++ b/49841_Intercuenca_Bajo_Huallaga/_raw_reportes_xlsx/IDConfig_65123_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4faffad6393449d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbc1537ecb0dc4f4e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2826 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.2402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.2902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.1102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.5502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.5802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.6102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.1902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.4902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.9802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.1702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.3902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.5902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.5002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.7402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.8202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.9802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.0302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.0802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.1102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.0002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.8202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.7702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.2702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.0002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.6902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.7902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
